--- a/Unity/Assets/Config/Excel/MapObjectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MapObjectConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="MapObjectProto" sheetId="1" r:id="rId1"/>
@@ -38,21 +38,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
-    <t>场景配置</t>
+    <t>MapConfig</t>
   </si>
   <si>
-    <t>MapConfig</t>
+    <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>场景配置</t>
   </si>
   <si>
     <t>HCFX_Beam_04&amp;0:0:0:10:10:10:0:0:0|-17:0:0:10:10:10:0:0:0|-85.03:0:0:10:10:10:326.21:124.1:0@HCFX_Appear_02_Start&amp;0:0:0:10:10:10:0:0:0@HCFX_Appear_03&amp;0:0:0:10:10:10:0:0:0|16:0:-30:10:10:10:0:0:0@</t>
@@ -68,13 +77,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -619,152 +634,158 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -862,8 +883,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C4:D6" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C4:D6" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="B1:C4" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:C4" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="MapConfig"/>
@@ -1159,43 +1180,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="45.5" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="45.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:4">
-      <c r="C3" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:4">
-      <c r="C4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:4">
-      <c r="C5" s="3" t="s">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:4">
-      <c r="C6" s="4">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>5</v>
+      <c r="C3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:3">
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
